--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2530-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2530-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E246D9DE-44B5-46F2-9B01-612F57FC6B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B2C3357-9325-47A5-B05F-32D8BC8E8536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{6BB94A75-E61F-4E00-B15E-B31A772CAA7E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{DC3DC4BB-97BA-478B-AB7C-7AC1B11531D2}"/>
   </bookViews>
   <sheets>
     <sheet name="2530-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1490,25 +1490,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE6C82C-2A72-4F54-83C9-DDAD4A179686}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDD7ABF1-32B0-449D-AD9A-17183C9FECD6}">
   <dimension ref="A1:R51"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1536,7 +1535,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1566,7 +1565,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1612,7 +1611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1662,7 +1661,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1716,7 +1715,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1772,7 +1771,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1828,7 +1827,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1884,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1940,7 +1939,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="40">
         <v>2024</v>
       </c>
@@ -1994,7 +1993,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2050,7 +2049,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2106,7 +2105,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2162,7 +2161,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2218,7 +2217,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="38">
         <v>2023</v>
       </c>
@@ -2272,7 +2271,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2328,7 +2327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2384,7 +2383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2440,7 +2439,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <v>2022</v>
       </c>
@@ -2494,7 +2493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>25</v>
       </c>
@@ -2550,7 +2549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2606,7 +2605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>2021</v>
       </c>
@@ -2660,7 +2659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>2020</v>
       </c>
@@ -2714,7 +2713,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="38">
         <v>2019</v>
       </c>
@@ -2768,7 +2767,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <v>2018</v>
       </c>
@@ -2822,7 +2821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="38">
         <v>2017</v>
       </c>
@@ -2876,7 +2875,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>2016</v>
       </c>
@@ -2930,7 +2929,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="38">
         <v>2015</v>
       </c>
@@ -2984,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="40">
         <v>2014</v>
       </c>
@@ -3038,7 +3037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="38">
         <v>2013</v>
       </c>
@@ -3092,7 +3091,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <v>2012</v>
       </c>
@@ -3146,7 +3145,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="38">
         <v>2011</v>
       </c>
@@ -3200,7 +3199,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <v>2010</v>
       </c>
@@ -3254,7 +3253,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="38">
         <v>2009</v>
       </c>
@@ -3308,7 +3307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <v>2008</v>
       </c>
@@ -3362,7 +3361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="38">
         <v>2007</v>
       </c>
@@ -3416,7 +3415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
         <v>2006</v>
       </c>
@@ -3470,7 +3469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="38">
         <v>2005</v>
       </c>
@@ -3524,7 +3523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="40">
         <v>2004</v>
       </c>
@@ -3578,7 +3577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="38">
         <v>2003</v>
       </c>
@@ -3632,7 +3631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="40">
         <v>2002</v>
       </c>
@@ -3686,7 +3685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="38">
         <v>2001</v>
       </c>
@@ -3740,7 +3739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="40">
         <v>2000</v>
       </c>
@@ -3794,7 +3793,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="38">
         <v>1999</v>
       </c>
@@ -3848,7 +3847,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="40">
         <v>1998</v>
       </c>
@@ -3902,7 +3901,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="38">
         <v>1997</v>
       </c>
@@ -3956,7 +3955,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="40">
         <v>1996</v>
       </c>
@@ -4010,7 +4009,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="38">
         <v>1995</v>
       </c>
@@ -4064,7 +4063,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="40">
         <v>1994</v>
       </c>
@@ -4118,7 +4117,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="38">
         <v>1993</v>
       </c>
@@ -4172,7 +4171,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="40" t="s">
         <v>48</v>
       </c>
